--- a/artfynd/A 4290-2026 artfynd.xlsx
+++ b/artfynd/A 4290-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,69 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124592542</v>
+        <v>93369761</v>
       </c>
       <c r="B2" t="n">
-        <v>100695</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224932</v>
+        <v>208242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig backsmörblomma</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gillsnäs NNO om, Srm</t>
+          <t>Stenstorp hage, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587822</v>
+        <v>587789</v>
       </c>
       <c r="R2" t="n">
-        <v>6547566</v>
+        <v>6547735</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +761,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,20 +789,15 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägslänt</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Chad Donaldson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Chad Donaldson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -786,12 +807,7 @@
         <v>124596158</v>
       </c>
       <c r="B3" t="n">
-        <v>105029</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,6 +909,216 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124592480</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gillsnäs NNO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>587822</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6547566</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägslänt skogsväg</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124592542</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101746</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>224932</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig backsmörblomma</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gillsnäs NNO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587822</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6547566</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4290-2026 artfynd.xlsx
+++ b/artfynd/A 4290-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93369761</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124596158</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124592480</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,8 +1138,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124592542</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>